--- a/VanHanhCD1/wwwroot/templates/BMVH_TB1ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_TB1ThieuKet1.xlsx
@@ -5,21 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\01. Keo Day\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2B7D2B-85AF-4664-9058-1E6960452EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C46B0D-C758-4598-ADB6-367F6518BBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4386788D-E345-4A72-8B59-F2B6CEDABEC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{4386788D-E345-4A72-8B59-F2B6CEDABEC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1265,14 +1274,21 @@
     <xf numFmtId="0" fontId="29" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1282,6 +1298,45 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1314,51 +1369,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1386,24 +1413,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2057,6 +2066,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6675FF-BF75-44D7-AB90-0DA1CBDADC48}">
   <dimension ref="A1:AP35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2064,248 +2076,248 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
-      <c r="X1" s="48" t="s">
+      <c r="X1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
-      <c r="AB1" s="49"/>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="49"/>
-      <c r="AP1" s="49"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="25"/>
     </row>
     <row r="2" spans="1:42" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="51"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="51"/>
-      <c r="AN2" s="51"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="51"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="27"/>
+      <c r="AP2" s="27"/>
     </row>
     <row r="3" spans="1:42" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="51"/>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="51"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
-      <c r="AL3" s="51"/>
-      <c r="AM3" s="51"/>
-      <c r="AN3" s="51"/>
-      <c r="AO3" s="51"/>
-      <c r="AP3" s="51"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
     </row>
     <row r="4" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="51"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="51"/>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="51"/>
-      <c r="AH4" s="51"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="51"/>
-      <c r="AM4" s="51"/>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="51"/>
-      <c r="AP4" s="51"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
     </row>
     <row r="6" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="55"/>
-      <c r="J6" s="56" t="s">
+      <c r="I6" s="36"/>
+      <c r="J6" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="45" t="s">
+      <c r="K6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="46" t="s">
+      <c r="L6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="45" t="s">
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="47" t="s">
+      <c r="P6" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="Q6" s="46" t="s">
+      <c r="Q6" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46" t="s">
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="U6" s="46"/>
-      <c r="V6" s="41" t="s">
+      <c r="U6" s="35"/>
+      <c r="V6" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="W6" s="41"/>
-      <c r="X6" s="41"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="41" t="s">
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="41" t="s">
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="34"/>
+      <c r="AE6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AF6" s="41"/>
-      <c r="AG6" s="41"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="42" t="s">
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="34"/>
+      <c r="AH6" s="34"/>
+      <c r="AI6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="44"/>
-      <c r="AM6" s="42" t="s">
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="40"/>
+      <c r="AM6" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="43"/>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="44"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="40"/>
     </row>
     <row r="7" spans="1:42" ht="57" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="41"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="34"/>
       <c r="D7" s="22" t="s">
         <v>71</v>
       </c>
@@ -2324,8 +2336,8 @@
       <c r="I7" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="J7" s="56"/>
-      <c r="K7" s="45"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="41"/>
       <c r="L7" s="22" t="s">
         <v>73</v>
       </c>
@@ -2335,8 +2347,8 @@
       <c r="N7" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="O7" s="45"/>
-      <c r="P7" s="47"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="42"/>
       <c r="Q7" s="23" t="s">
         <v>73</v>
       </c>
@@ -2417,7 +2429,7 @@
       </c>
     </row>
     <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="6" t="s">
         <v>23</v>
       </c>
@@ -2543,7 +2555,7 @@
       </c>
     </row>
     <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="11" t="s">
         <v>34</v>
       </c>
@@ -2688,7 +2700,7 @@
       </c>
     </row>
     <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="11" t="s">
         <v>35</v>
       </c>
@@ -2833,7 +2845,7 @@
       </c>
     </row>
     <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="11" t="s">
         <v>36</v>
       </c>
@@ -2978,7 +2990,7 @@
       </c>
     </row>
     <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="11" t="s">
         <v>37</v>
       </c>
@@ -3123,7 +3135,7 @@
       </c>
     </row>
     <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="11" t="s">
         <v>38</v>
       </c>
@@ -3268,7 +3280,7 @@
       </c>
     </row>
     <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="11" t="s">
         <v>39</v>
       </c>
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="11" t="s">
         <v>40</v>
       </c>
@@ -3558,7 +3570,7 @@
       </c>
     </row>
     <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="11" t="s">
         <v>41</v>
       </c>
@@ -3703,7 +3715,7 @@
       </c>
     </row>
     <row r="17" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="11" t="s">
         <v>42</v>
       </c>
@@ -3848,7 +3860,7 @@
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="14" t="s">
         <v>43</v>
       </c>
@@ -3993,7 +4005,7 @@
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
@@ -4138,7 +4150,7 @@
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="14" t="s">
         <v>45</v>
       </c>
@@ -4283,7 +4295,7 @@
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="14" t="s">
         <v>46</v>
       </c>
@@ -4430,7 +4442,7 @@
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="14" t="s">
         <v>48</v>
       </c>
@@ -4577,7 +4589,7 @@
       </c>
     </row>
     <row r="23" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="14" t="s">
         <v>49</v>
       </c>
@@ -4724,7 +4736,7 @@
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="14" t="s">
         <v>50</v>
       </c>
@@ -4871,7 +4883,7 @@
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="14" t="s">
         <v>51</v>
       </c>
@@ -5018,7 +5030,7 @@
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
+      <c r="A26" s="31"/>
       <c r="B26" s="14" t="s">
         <v>52</v>
       </c>
@@ -5165,7 +5177,7 @@
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="14" t="s">
         <v>53</v>
       </c>
@@ -5312,7 +5324,7 @@
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="14" t="s">
         <v>54</v>
       </c>
@@ -5459,7 +5471,7 @@
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="14" t="s">
         <v>55</v>
       </c>
@@ -5606,7 +5618,7 @@
       </c>
     </row>
     <row r="30" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="14" t="s">
         <v>56</v>
       </c>
@@ -5753,7 +5765,7 @@
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="14" t="s">
         <v>57</v>
       </c>
@@ -5900,7 +5912,7 @@
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="14" t="s">
         <v>58</v>
       </c>
@@ -6047,161 +6059,183 @@
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="31"/>
-      <c r="Z33" s="31"/>
-      <c r="AA33" s="31"/>
-      <c r="AB33" s="31"/>
-      <c r="AC33" s="31"/>
-      <c r="AD33" s="31"/>
-      <c r="AE33" s="31"/>
-      <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-      <c r="AH33" s="31"/>
-      <c r="AI33" s="31"/>
-      <c r="AJ33" s="31"/>
-      <c r="AK33" s="31"/>
-      <c r="AL33" s="31"/>
-      <c r="AM33" s="31"/>
-      <c r="AN33" s="31"/>
-      <c r="AO33" s="31"/>
-      <c r="AP33" s="31"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="47"/>
+      <c r="N33" s="47"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="47"/>
+      <c r="Q33" s="47"/>
+      <c r="R33" s="47"/>
+      <c r="S33" s="47"/>
+      <c r="T33" s="47"/>
+      <c r="U33" s="47"/>
+      <c r="V33" s="47"/>
+      <c r="W33" s="47"/>
+      <c r="X33" s="47"/>
+      <c r="Y33" s="47"/>
+      <c r="Z33" s="47"/>
+      <c r="AA33" s="47"/>
+      <c r="AB33" s="47"/>
+      <c r="AC33" s="47"/>
+      <c r="AD33" s="47"/>
+      <c r="AE33" s="47"/>
+      <c r="AF33" s="47"/>
+      <c r="AG33" s="47"/>
+      <c r="AH33" s="47"/>
+      <c r="AI33" s="47"/>
+      <c r="AJ33" s="47"/>
+      <c r="AK33" s="47"/>
+      <c r="AL33" s="47"/>
+      <c r="AM33" s="47"/>
+      <c r="AN33" s="47"/>
+      <c r="AO33" s="47"/>
+      <c r="AP33" s="47"/>
     </row>
     <row r="34" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="38" t="s">
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="24" t="s">
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="55"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
-      <c r="S34" s="25"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="32" t="s">
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="44"/>
+      <c r="S34" s="44"/>
+      <c r="T34" s="45"/>
+      <c r="U34" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="24" t="s">
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="50"/>
+      <c r="Y34" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AF34" s="25"/>
-      <c r="AG34" s="26"/>
-      <c r="AH34" s="24" t="s">
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="44"/>
+      <c r="AB34" s="44"/>
+      <c r="AC34" s="44"/>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="44"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="45"/>
+      <c r="AH34" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="AI34" s="25"/>
-      <c r="AJ34" s="25"/>
-      <c r="AK34" s="25"/>
-      <c r="AL34" s="25"/>
-      <c r="AM34" s="25"/>
-      <c r="AN34" s="25"/>
-      <c r="AO34" s="25"/>
-      <c r="AP34" s="26"/>
+      <c r="AI34" s="44"/>
+      <c r="AJ34" s="44"/>
+      <c r="AK34" s="44"/>
+      <c r="AL34" s="44"/>
+      <c r="AM34" s="44"/>
+      <c r="AN34" s="44"/>
+      <c r="AO34" s="44"/>
+      <c r="AP34" s="45"/>
     </row>
     <row r="35" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="38" t="s">
+      <c r="A35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="24" t="s">
+      <c r="E35" s="55"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="M35" s="25"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
-      <c r="S35" s="25"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="35"/>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="37"/>
-      <c r="Y35" s="24" t="s">
+      <c r="M35" s="44"/>
+      <c r="N35" s="45"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="44"/>
+      <c r="Q35" s="44"/>
+      <c r="R35" s="44"/>
+      <c r="S35" s="44"/>
+      <c r="T35" s="45"/>
+      <c r="U35" s="51"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="53"/>
+      <c r="Y35" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="24"/>
-      <c r="AC35" s="25"/>
-      <c r="AD35" s="25"/>
-      <c r="AE35" s="25"/>
-      <c r="AF35" s="25"/>
-      <c r="AG35" s="26"/>
-      <c r="AH35" s="24" t="s">
+      <c r="Z35" s="44"/>
+      <c r="AA35" s="45"/>
+      <c r="AB35" s="43"/>
+      <c r="AC35" s="44"/>
+      <c r="AD35" s="44"/>
+      <c r="AE35" s="44"/>
+      <c r="AF35" s="44"/>
+      <c r="AG35" s="45"/>
+      <c r="AH35" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="AI35" s="25"/>
-      <c r="AJ35" s="26"/>
-      <c r="AK35" s="24"/>
-      <c r="AL35" s="25"/>
-      <c r="AM35" s="25"/>
-      <c r="AN35" s="25"/>
-      <c r="AO35" s="25"/>
-      <c r="AP35" s="26"/>
+      <c r="AI35" s="44"/>
+      <c r="AJ35" s="45"/>
+      <c r="AK35" s="43"/>
+      <c r="AL35" s="44"/>
+      <c r="AM35" s="44"/>
+      <c r="AN35" s="44"/>
+      <c r="AO35" s="44"/>
+      <c r="AP35" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="AH35:AJ35"/>
+    <mergeCell ref="AI6:AL6"/>
+    <mergeCell ref="AK35:AP35"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="A33:AP33"/>
+    <mergeCell ref="A34:C35"/>
+    <mergeCell ref="D34:K34"/>
+    <mergeCell ref="L34:T34"/>
+    <mergeCell ref="U34:X35"/>
+    <mergeCell ref="Y34:AG34"/>
+    <mergeCell ref="AH34:AP34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:T35"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="AB35:AG35"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="A9:A20"/>
     <mergeCell ref="X1:AP1"/>
     <mergeCell ref="A2:AP2"/>
     <mergeCell ref="A3:AP3"/>
@@ -6218,28 +6252,6 @@
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:Z6"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A9:A20"/>
-    <mergeCell ref="AI6:AL6"/>
-    <mergeCell ref="AK35:AP35"/>
-    <mergeCell ref="A21:A32"/>
-    <mergeCell ref="A33:AP33"/>
-    <mergeCell ref="A34:C35"/>
-    <mergeCell ref="D34:K34"/>
-    <mergeCell ref="L34:T34"/>
-    <mergeCell ref="U34:X35"/>
-    <mergeCell ref="Y34:AG34"/>
-    <mergeCell ref="AH34:AP34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:T35"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="AB35:AG35"/>
-    <mergeCell ref="AH35:AJ35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6257,9 +6269,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="68"/>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
+      <c r="A1" s="57"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
@@ -6274,58 +6286,58 @@
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="69" t="s">
+      <c r="R1" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="68"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="15"/>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="71" t="s">
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="15"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
       <c r="T3" s="15"/>
@@ -6357,10 +6369,10 @@
       <c r="U4" s="17"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="61"/>
+      <c r="B5" s="67"/>
       <c r="C5" s="18" t="s">
         <v>69</v>
       </c>
@@ -6508,10 +6520,10 @@
       <c r="AA7" s="19"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="67"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="20" t="s">
         <v>143</v>
       </c>
@@ -6541,7 +6553,7 @@
       <c r="AA8" s="19"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="63" t="s">
         <v>75</v>
       </c>
       <c r="B9" s="19" t="s">
@@ -6576,7 +6588,7 @@
       <c r="AA9" s="19"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="19" t="s">
         <v>76</v>
       </c>
@@ -6609,7 +6621,7 @@
       <c r="AA10" s="19"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="19" t="s">
         <v>71</v>
       </c>
@@ -6642,10 +6654,10 @@
       <c r="AA11" s="19"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="67"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="20" t="s">
         <v>113</v>
       </c>
@@ -6675,7 +6687,7 @@
       <c r="AA12" s="19"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="63" t="s">
         <v>78</v>
       </c>
       <c r="B13" s="19" t="s">
@@ -6710,7 +6722,7 @@
       <c r="AA13" s="19"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="58"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="19" t="s">
         <v>76</v>
       </c>
@@ -6743,7 +6755,7 @@
       <c r="AA14" s="19"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="19" t="s">
         <v>79</v>
       </c>
@@ -6776,7 +6788,7 @@
       <c r="AA15" s="19"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="63" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="19" t="s">
@@ -6811,7 +6823,7 @@
       <c r="AA16" s="19"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="59"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="19" t="s">
         <v>82</v>
       </c>
@@ -6844,7 +6856,7 @@
       <c r="AA17" s="19"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="63" t="s">
         <v>83</v>
       </c>
       <c r="B18" s="19" t="s">
@@ -6879,7 +6891,7 @@
       <c r="AA18" s="19"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="58"/>
+      <c r="A19" s="64"/>
       <c r="B19" s="19" t="s">
         <v>85</v>
       </c>
@@ -6912,7 +6924,7 @@
       <c r="AA19" s="19"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="58"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="19" t="s">
         <v>86</v>
       </c>
@@ -6945,7 +6957,7 @@
       <c r="AA20" s="19"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
+      <c r="A21" s="64"/>
       <c r="B21" s="19" t="s">
         <v>87</v>
       </c>
@@ -6978,7 +6990,7 @@
       <c r="AA21" s="19"/>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="19" t="s">
         <v>88</v>
       </c>
@@ -7011,7 +7023,7 @@
       <c r="AA22" s="19"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="63" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="19" t="s">
@@ -7046,7 +7058,7 @@
       <c r="AA23" s="19"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="58"/>
+      <c r="A24" s="64"/>
       <c r="B24" s="19" t="s">
         <v>91</v>
       </c>
@@ -7079,7 +7091,7 @@
       <c r="AA24" s="19"/>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
+      <c r="A25" s="64"/>
       <c r="B25" s="19" t="s">
         <v>92</v>
       </c>
@@ -7112,7 +7124,7 @@
       <c r="AA25" s="19"/>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="19" t="s">
         <v>93</v>
       </c>
@@ -7145,7 +7157,7 @@
       <c r="AA26" s="19"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="63" t="s">
         <v>94</v>
       </c>
       <c r="B27" s="19" t="s">
@@ -7180,7 +7192,7 @@
       <c r="AA27" s="19"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" s="58"/>
+      <c r="A28" s="64"/>
       <c r="B28" s="19" t="s">
         <v>96</v>
       </c>
@@ -7213,7 +7225,7 @@
       <c r="AA28" s="19"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A29" s="58"/>
+      <c r="A29" s="64"/>
       <c r="B29" s="19" t="s">
         <v>97</v>
       </c>
@@ -7246,7 +7258,7 @@
       <c r="AA29" s="19"/>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
+      <c r="A30" s="65"/>
       <c r="B30" s="19" t="s">
         <v>98</v>
       </c>
@@ -7279,7 +7291,7 @@
       <c r="AA30" s="19"/>
     </row>
     <row r="31" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="68" t="s">
         <v>99</v>
       </c>
       <c r="B31" s="19" t="s">
@@ -7314,7 +7326,7 @@
       <c r="AA31" s="19"/>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" s="62"/>
+      <c r="A32" s="68"/>
       <c r="B32" s="19" t="s">
         <v>101</v>
       </c>
@@ -7347,7 +7359,7 @@
       <c r="AA32" s="19"/>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="62"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="19" t="s">
         <v>102</v>
       </c>
@@ -7380,7 +7392,7 @@
       <c r="AA33" s="19"/>
     </row>
     <row r="34" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="62"/>
+      <c r="A34" s="68"/>
       <c r="B34" s="19" t="s">
         <v>103</v>
       </c>
@@ -7413,7 +7425,7 @@
       <c r="AA34" s="19"/>
     </row>
     <row r="35" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="69" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="19" t="s">
@@ -7448,7 +7460,7 @@
       <c r="AA35" s="19"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="64"/>
+      <c r="A36" s="70"/>
       <c r="B36" s="19" t="s">
         <v>105</v>
       </c>
@@ -7481,7 +7493,7 @@
       <c r="AA36" s="19"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="64"/>
+      <c r="A37" s="70"/>
       <c r="B37" s="19" t="s">
         <v>106</v>
       </c>
@@ -7514,7 +7526,7 @@
       <c r="AA37" s="19"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="65"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="19" t="s">
         <v>107</v>
       </c>
@@ -7550,11 +7562,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="E2:Q3"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A31:A34"/>
@@ -7565,6 +7572,11 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="E2:Q3"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
